--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_19-12-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_19-12-2025.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£23.87</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£27.67</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£29.74</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£32.42</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>£35.91</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£39.12</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£46.64</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£46.55</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£51.7</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£57.31</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£49.55</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1615,24 +1615,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/celotex-xr4000-insulation-pitched-roof-board-1200-x-2400mm?variant=55597620396416 (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>£31.00</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>£30.4</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>£30.45</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>£31.00</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>£30.4</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>£30.45</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>£30.27</t>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£74.18</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£81.55</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£86.21</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£89.87</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -1993,17 +1993,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£660.25</t>
+          <t>£690.00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>£660.25</t>
+          <t>£690.00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>£660.25</t>
+          <t>£690.00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2090,17 +2090,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>£850.25</t>
+          <t>£890.00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>£850.25</t>
+          <t>£890.00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>£850.25</t>
+          <t>£890.00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2187,17 +2187,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>£25.58</t>
+          <t>£26.89</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>£25.58</t>
+          <t>£26.89</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>£25.58</t>
+          <t>£26.89</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£51.2</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2284,17 +2284,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>£31.30</t>
+          <t>£31.63</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>£31.30</t>
+          <t>£31.63</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>£31.30</t>
+          <t>£31.63</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>£44.24</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£59.2</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2381,17 +2381,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>£34.15</t>
+          <t>£35.57</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>£34.15</t>
+          <t>£35.57</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>£34.15</t>
+          <t>£35.57</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£79.58</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2478,17 +2478,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>£38.90</t>
+          <t>£40.45</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>£38.90</t>
+          <t>£40.45</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>£38.90</t>
+          <t>£40.45</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>£55.49</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>£92.82</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£70.18</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2575,17 +2575,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>£41.23</t>
+          <t>£43.40</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>£41.23</t>
+          <t>£43.40</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>£41.23</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>£41.25</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2672,17 +2672,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>£41.33</t>
+          <t>£43.50</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>£41.33</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>£41.33</t>
+          <t>£43.50</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>£40.57</t>
+          <t>£42.70</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>£40.57</t>
+          <t>£42.70</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>£40.57</t>
+          <t>£42.70</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2963,17 +2963,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>£1,043.92</t>
+          <t>£1,110.00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>£1,043.92</t>
+          <t>£1,110.00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>£1,110.00</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>£1057.71</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>£1948.16</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3060,17 +3060,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>£1,127.79</t>
+          <t>£1,218.00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>£1,127.79</t>
+          <t>£1,218.00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>£1,200.00</t>
+          <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3115,12 +3115,12 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>£1126.15</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>£2157.92</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3157,17 +3157,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>£1,096.48</t>
+          <t>£1,220.00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>£1,096.48</t>
+          <t>£1,220.00</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>£1,160.00</t>
+          <t>£1,220.00</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
